--- a/OMOP Analysis/Results/Overall/overall_combined_bootstrap_summary_costs_OMOP.xlsx
+++ b/OMOP Analysis/Results/Overall/overall_combined_bootstrap_summary_costs_OMOP.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -418,145 +418,71 @@
         </is>
       </c>
       <c r="B2">
-        <v>792.951</v>
+        <v>1087.052</v>
       </c>
       <c r="C2">
-        <v>28.132</v>
+        <v>54.989</v>
       </c>
       <c r="D2">
-        <v>5.304</v>
+        <v>7.415</v>
       </c>
       <c r="E2">
-        <v>0.168</v>
+        <v>0.234</v>
       </c>
       <c r="F2">
-        <v>782.672</v>
+        <v>1072.669</v>
       </c>
       <c r="G2">
-        <v>803.4640000000001</v>
+        <v>1101.737</v>
       </c>
       <c r="H2">
-        <v>782.343</v>
+        <v>1072.003</v>
       </c>
       <c r="I2">
-        <v>803.472</v>
+        <v>1101.713</v>
       </c>
       <c r="J2">
-        <v>782.547</v>
+        <v>1072.543</v>
       </c>
       <c r="K2">
-        <v>803.677</v>
+        <v>1102.253</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>All Patients &amp; relevant encounters</t>
+          <t>Users &amp; all encounters</t>
         </is>
       </c>
       <c r="B3">
-        <v>689.404</v>
+        <v>1116.378</v>
       </c>
       <c r="C3">
-        <v>23.25</v>
+        <v>61.426</v>
       </c>
       <c r="D3">
-        <v>4.822</v>
+        <v>7.837</v>
       </c>
       <c r="E3">
-        <v>0.152</v>
+        <v>0.248</v>
       </c>
       <c r="F3">
-        <v>680.083</v>
+        <v>1100.161</v>
       </c>
       <c r="G3">
-        <v>698.985</v>
+        <v>1130.883</v>
       </c>
       <c r="H3">
-        <v>679.467</v>
+        <v>1101.295</v>
       </c>
       <c r="I3">
-        <v>699.001</v>
+        <v>1132.087</v>
       </c>
       <c r="J3">
-        <v>679.937</v>
+        <v>1099.813</v>
       </c>
       <c r="K3">
-        <v>699.471</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Users &amp; all encounters</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>816.479</v>
-      </c>
-      <c r="C4">
-        <v>27.79</v>
-      </c>
-      <c r="D4">
-        <v>5.272</v>
-      </c>
-      <c r="E4">
-        <v>0.167</v>
-      </c>
-      <c r="F4">
-        <v>806.318</v>
-      </c>
-      <c r="G4">
-        <v>826.982</v>
-      </c>
-      <c r="H4">
-        <v>806.378</v>
-      </c>
-      <c r="I4">
-        <v>826.793</v>
-      </c>
-      <c r="J4">
-        <v>806.337</v>
-      </c>
-      <c r="K4">
-        <v>826.752</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Users &amp; relevant encounters</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>710.54</v>
-      </c>
-      <c r="C5">
-        <v>22.702</v>
-      </c>
-      <c r="D5">
-        <v>4.765</v>
-      </c>
-      <c r="E5">
-        <v>0.151</v>
-      </c>
-      <c r="F5">
-        <v>701.3869999999999</v>
-      </c>
-      <c r="G5">
-        <v>720.0650000000001</v>
-      </c>
-      <c r="H5">
-        <v>701.287</v>
-      </c>
-      <c r="I5">
-        <v>719.7859999999999</v>
-      </c>
-      <c r="J5">
-        <v>701.48</v>
-      </c>
-      <c r="K5">
-        <v>719.98</v>
+        <v>1130.605</v>
       </c>
     </row>
   </sheetData>
